--- a/docs/StructureDefinition-SpaceEquipment.xlsx
+++ b/docs/StructureDefinition-SpaceEquipment.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.6</t>
+    <t>0.5.8</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-30T19:11:20-07:00</t>
+    <t>2026-02-02T11:11:20-06:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-SpaceEquipment.xlsx
+++ b/docs/StructureDefinition-SpaceEquipment.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.8</t>
+    <t>0.5.9</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-02T11:11:20-06:00</t>
+    <t>2026-02-04T10:26:00-06:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-SpaceEquipment.xlsx
+++ b/docs/StructureDefinition-SpaceEquipment.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.12</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T00:24:16-05:00</t>
+    <t>2026-05-25T15:07:02-06:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-SpaceEquipment.xlsx
+++ b/docs/StructureDefinition-SpaceEquipment.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.6.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T15:07:02-06:00</t>
+    <t>2026-08-03T22:31:50-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
